--- a/docs/00_基礎/GitHubについて.xlsx
+++ b/docs/00_基礎/GitHubについて.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishikawaaoi/workspace_study/docs/00_基礎/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15264E6E-9551-5D42-BBB7-F64D3832E383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03ADD51-0795-D74A-930F-753A5290B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16460" activeTab="5" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" activeTab="5" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
   </bookViews>
   <sheets>
     <sheet name="GitHub基礎" sheetId="11" r:id="rId1"/>

--- a/docs/00_基礎/GitHubについて.xlsx
+++ b/docs/00_基礎/GitHubについて.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishikawaaoi/workspace_study/docs/00_基礎/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03ADD51-0795-D74A-930F-753A5290B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4471C45-E932-8B4E-B2B9-5299C5095AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" activeTab="5" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
   </bookViews>
   <sheets>
     <sheet name="GitHub基礎" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="311">
   <si>
     <t>main</t>
   </si>
@@ -1571,41 +1571,95 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>もしよければ、私が </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+    <t>git commit -m "first commit springboot environment"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git reset</t>
+  </si>
+  <si>
+    <t>「add（送信待ちのリスト化）」→「commit（記録）」→「push（送信）」</t>
+    <rPh sb="5" eb="8">
+      <t>ソウシn</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t xml:space="preserve">カ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git add .</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git commit-m "コメント"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git push</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>find . -name .DS_Store -delete</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">git add </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
-        <color rgb="FF000000"/>
+        <color theme="9"/>
         <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>一発でこの手順を実行できるシェルスクリプト形式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> にまとめて渡すこともできます。</t>
-    </r>
-  </si>
-  <si>
-    <t>そうすればコピペだけで作り直し完了です。</t>
-  </si>
-  <si>
-    <t>作りますか？</t>
-  </si>
-  <si>
-    <t>git commit -m "first commit springboot environment"</t>
+      </rPr>
+      <t>webgame/src</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信待ちのリストの削除</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシn</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">マチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一部をリスト化</t>
+    <rPh sb="0" eb="2">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">カ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全てをリスト化</t>
+    <rPh sb="0" eb="1">
+      <t>スベテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的にはこれを使う</t>
+    <rPh sb="0" eb="3">
+      <t>キホn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Macの場合勝手に作られる.DS_Storeファイルを削除する。</t>
+    <rPh sb="6" eb="8">
+      <t>カッテ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクジョ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1613,7 +1667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1723,6 +1777,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1732,7 +1793,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1741,11 +1802,48 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="hair">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1754,7 +1852,7 @@
     <border>
       <left/>
       <right/>
-      <top style="hair">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1762,22 +1860,22 @@
     </border>
     <border>
       <left/>
-      <right style="hair">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="hair">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="hair">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1786,73 +1884,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="hair">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="hair">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1866,7 +1909,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1912,7 +1955,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
@@ -1924,22 +1967,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
@@ -3746,7 +3777,7 @@
     </row>
     <row r="81" spans="2:3">
       <c r="C81" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="85" spans="2:3" ht="40">
@@ -3960,465 +3991,512 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29287DF5-21CC-7D4B-BB9B-06DAB6E5204E}">
-  <dimension ref="B2:Y33"/>
+  <dimension ref="B2:Y56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.7109375" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:25" ht="31">
-      <c r="B2" s="11" t="s">
+    <row r="2" spans="2:17">
+      <c r="B2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="B4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="C6" t="s">
+        <v>310</v>
+      </c>
+      <c r="P6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="C7" t="s">
+        <v>308</v>
+      </c>
+      <c r="P7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="C8" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="C9" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="P10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="P11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" ht="31">
+      <c r="B25" s="11" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="4" spans="2:25">
-      <c r="B4" s="12" t="s">
+    <row r="27" spans="2:25">
+      <c r="B27" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="12" t="s">
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="14"/>
-    </row>
-    <row r="5" spans="2:25">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="25" t="s">
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="17"/>
+    </row>
+    <row r="28" spans="2:25">
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="20"/>
-    </row>
-    <row r="6" spans="2:25">
-      <c r="B6" s="12" t="s">
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" spans="2:25">
+      <c r="B29" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="12" t="s">
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="14"/>
-    </row>
-    <row r="7" spans="2:25">
-      <c r="B7" s="21" t="s">
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="17"/>
+    </row>
+    <row r="30" spans="2:25">
+      <c r="B30" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="21" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="17"/>
-    </row>
-    <row r="8" spans="2:25">
-      <c r="B8" s="12" t="s">
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" spans="2:25">
+      <c r="B31" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="12" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="14"/>
-    </row>
-    <row r="9" spans="2:25">
-      <c r="B9" s="21" t="s">
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="17"/>
+    </row>
+    <row r="32" spans="2:25">
+      <c r="B32" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="21" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="17"/>
-    </row>
-    <row r="10" spans="2:25">
-      <c r="B10" s="12" t="s">
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="20"/>
+    </row>
+    <row r="33" spans="2:25">
+      <c r="B33" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="12" t="s">
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="14"/>
-    </row>
-    <row r="11" spans="2:25">
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="21" t="s">
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="17"/>
+    </row>
+    <row r="34" spans="2:25">
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="17"/>
-    </row>
-    <row r="12" spans="2:25">
-      <c r="B12" s="22" t="s">
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="20"/>
+    </row>
+    <row r="35" spans="2:25">
+      <c r="B35" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="22" t="s">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="24"/>
-    </row>
-    <row r="13" spans="2:25">
-      <c r="B13" s="22" t="s">
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="14"/>
+    </row>
+    <row r="36" spans="2:25">
+      <c r="B36" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="22" t="s">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="24"/>
-    </row>
-    <row r="14" spans="2:25">
-      <c r="B14" s="22" t="s">
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="14"/>
+    </row>
+    <row r="37" spans="2:25">
+      <c r="B37" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="22" t="s">
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="24"/>
-    </row>
-    <row r="15" spans="2:25">
-      <c r="B15" s="12" t="s">
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="14"/>
+    </row>
+    <row r="38" spans="2:25">
+      <c r="B38" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="12" t="s">
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="14"/>
-    </row>
-    <row r="16" spans="2:25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="21" t="s">
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16"/>
+      <c r="Y38" s="17"/>
+    </row>
+    <row r="39" spans="2:25">
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="17"/>
-    </row>
-    <row r="17" spans="2:25">
-      <c r="B17" s="22" t="s">
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="20"/>
+    </row>
+    <row r="40" spans="2:25">
+      <c r="B40" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="22" t="s">
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="24"/>
-    </row>
-    <row r="20" spans="2:25" ht="24">
-      <c r="B20" s="9" t="s">
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="14"/>
+    </row>
+    <row r="43" spans="2:25" ht="24">
+      <c r="B43" s="9" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="22" spans="2:25">
-      <c r="B22" s="1" t="s">
+    <row r="45" spans="2:25">
+      <c r="B45" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="24" spans="2:25">
-      <c r="B24" s="1" t="s">
+    <row r="47" spans="2:25">
+      <c r="B47" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="26" spans="2:25">
-      <c r="B26" s="8" t="s">
+    <row r="49" spans="2:2">
+      <c r="B49" s="8" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="2:25">
-      <c r="B30" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25">
-      <c r="B31" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="1" t="s">
-        <v>300</v>
-      </c>
+    <row r="53" spans="2:2">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/docs/00_基礎/GitHubについて.xlsx
+++ b/docs/00_基礎/GitHubについて.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishikawaaoi/workspace_study/docs/00_基礎/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4471C45-E932-8B4E-B2B9-5299C5095AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4479E1-4F2A-5546-84F9-CC72656274EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="6" xr2:uid="{88A5724A-B7E1-0A49-9353-B96C2BC3D0EE}"/>
   </bookViews>
   <sheets>
     <sheet name="GitHub基礎" sheetId="11" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="リポジトリの作成" sheetId="13" r:id="rId3"/>
     <sheet name="ターミナル▶︎" sheetId="16" r:id="rId4"/>
     <sheet name="環境構築" sheetId="12" r:id="rId5"/>
-    <sheet name="コマンド集" sheetId="14" r:id="rId6"/>
+    <sheet name="サボりコマンド集" sheetId="14" r:id="rId6"/>
+    <sheet name="コマンド一覧" sheetId="17" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="488">
   <si>
     <t>main</t>
   </si>
@@ -1373,9 +1374,6 @@
     </r>
   </si>
   <si>
-    <t>安全コマンド集（順番に実行）</t>
-  </si>
-  <si>
     <t># 1️⃣ 新しいディレクトリを作成して移動</t>
   </si>
   <si>
@@ -1431,9 +1429,6 @@
   </si>
   <si>
     <t># 8️⃣ リモートリポジトリを設定</t>
-  </si>
-  <si>
-    <t>git remote add origin https://github.com/aoaoaoao143/リポジトリ名.git</t>
   </si>
   <si>
     <t># 9️⃣ GitHub に push</t>
@@ -1575,90 +1570,653 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>git reset</t>
-  </si>
-  <si>
-    <t>「add（送信待ちのリスト化）」→「commit（記録）」→「push（送信）」</t>
-    <rPh sb="5" eb="8">
-      <t>ソウシn</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t xml:space="preserve">カ </t>
+    <t>コマンド</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>イメージ</t>
+  </si>
+  <si>
+    <t>ファイルを「保存対象」に入れる</t>
+  </si>
+  <si>
+    <t>荷物を箱に詰める</t>
+  </si>
+  <si>
+    <t>変更を「記録」する</t>
+  </si>
+  <si>
+    <t>箱に封をしてラベルを貼る</t>
+  </si>
+  <si>
+    <t>git push</t>
+  </si>
+  <si>
+    <t>記録を「サーバー」に送る</t>
+  </si>
+  <si>
+    <t>荷物をトラックで発送する</t>
+  </si>
+  <si>
+    <t>今の状態（変更点）を確認する</t>
+  </si>
+  <si>
+    <t>発送前の荷物リストを見る</t>
+  </si>
+  <si>
+    <t>これまでのコミット履歴を見る</t>
+  </si>
+  <si>
+    <t>過去の発送伝票を眺める</t>
+  </si>
+  <si>
+    <t>ファイルの「差分」を見る</t>
+  </si>
+  <si>
+    <t>どこを書き換えたか比較する</t>
+  </si>
+  <si>
+    <t>特定のコミットの詳細を見る</t>
+  </si>
+  <si>
+    <t>1つ前の作業内容を覗く</t>
+  </si>
+  <si>
+    <t>2. 過去に戻る・確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 超基本：毎日の「保存と送信」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. 枝分かれ（ブランチ）と合流</t>
+  </si>
+  <si>
+    <t>ブランチの一覧を見る・作る</t>
+  </si>
+  <si>
+    <t>今どの道（枝）にいるか確認</t>
+  </si>
+  <si>
+    <t>ブランチを切り替える</t>
+  </si>
+  <si>
+    <t>他のブランチを合流させる</t>
+  </si>
+  <si>
+    <t>枝Aの内容を枝Bに取り込む</t>
+  </si>
+  <si>
+    <t>4. サーバー（GitHub等）とのやり取り</t>
+  </si>
+  <si>
+    <t>サーバーの最新版を取ってくる</t>
+  </si>
+  <si>
+    <t>他の人の作業を自分のPCへ</t>
+  </si>
+  <si>
+    <t>サーバーの情報だけ確認する</t>
+  </si>
+  <si>
+    <t>荷物は取らず、状況だけ見る</t>
+  </si>
+  <si>
+    <t>サーバーのリポジトリを丸ごと複製</t>
+  </si>
+  <si>
+    <t>最初の一回だけ実行する</t>
+  </si>
+  <si>
+    <t>送信先（origin等）を確認・設定</t>
+  </si>
+  <si>
+    <t>通信相手の住所録</t>
+  </si>
+  <si>
+    <t>5. 困った時・やり直したい時</t>
+  </si>
+  <si>
+    <t>コミットを取り消す</t>
+  </si>
+  <si>
+    <t>封をした箱をもう一度開ける</t>
+  </si>
+  <si>
+    <t>打ち消しのコミットを作る</t>
+  </si>
+  <si>
+    <t>履歴を残したまま間違いを正す</t>
+  </si>
+  <si>
+    <t>作業を一時的に「避難」させる</t>
+  </si>
+  <si>
+    <t>机の上の道具を引出しに隠す</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>commit</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>checkout</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>merge</t>
+  </si>
+  <si>
+    <t>switch</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>fetch</t>
+  </si>
+  <si>
+    <t>clone</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>reset</t>
+  </si>
+  <si>
+    <t>revert</t>
+  </si>
+  <si>
+    <t>stash</t>
+  </si>
+  <si>
+    <t>git</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>--all</t>
+  </si>
+  <si>
+    <t>削除されたファイルも含め全て追加</t>
+  </si>
+  <si>
+    <t>--dry-run</t>
+  </si>
+  <si>
+    <t>実際に追加せず、何が追加されるか試す</t>
+  </si>
+  <si>
+    <t>--message</t>
+  </si>
+  <si>
+    <t>コミットメッセージを指定</t>
+  </si>
+  <si>
+    <t>--amend</t>
+  </si>
+  <si>
+    <t>直前のコミットをやり直す（修正）</t>
+  </si>
+  <si>
+    <t>変更があったファイルを自動でaddしてコミット</t>
+  </si>
+  <si>
+    <t>--short</t>
+  </si>
+  <si>
+    <t>短い形式で状態を表示</t>
+  </si>
+  <si>
+    <t>--branch</t>
+  </si>
+  <si>
+    <t>現在のブランチ情報も表示</t>
+  </si>
+  <si>
+    <t>--oneline</t>
+  </si>
+  <si>
+    <t>各コミットを1行で表示</t>
+  </si>
+  <si>
+    <t>--graph</t>
+  </si>
+  <si>
+    <t>枝分かれの状態をアスキーアートで表示</t>
+  </si>
+  <si>
+    <t>全てのブランチの履歴を表示</t>
+  </si>
+  <si>
+    <t>--name-only</t>
+  </si>
+  <si>
+    <t>変更されたファイル名だけ表示</t>
+  </si>
+  <si>
+    <t>--stat</t>
+  </si>
+  <si>
+    <t>変更された行数の統計を表示</t>
+  </si>
+  <si>
+    <t>--format</t>
+  </si>
+  <si>
+    <t>出力フォーマットをカスタマイズ</t>
+  </si>
+  <si>
+    <t>--cached (or --staged)</t>
+  </si>
+  <si>
+    <t>add した後の変更点を見る</t>
+  </si>
+  <si>
+    <t>checkout の現代版（推奨）</t>
+  </si>
+  <si>
+    <t>新しいブランチを作成して切り替え</t>
+  </si>
+  <si>
+    <t>--force</t>
+  </si>
+  <si>
+    <t>未保存の変更を捨てて強制切り替え</t>
+  </si>
+  <si>
+    <t>--list</t>
+  </si>
+  <si>
+    <t>ブランチの一覧を表示（デフォルト）</t>
+  </si>
+  <si>
+    <t>--delete</t>
+  </si>
+  <si>
+    <t>指定したブランチを削除</t>
+  </si>
+  <si>
+    <t>--move</t>
+  </si>
+  <si>
+    <t>ブランチの名前を変更</t>
+  </si>
+  <si>
+    <t>--create</t>
+  </si>
+  <si>
+    <t>--discard-changes</t>
+  </si>
+  <si>
+    <t>変更を捨てて切り替える</t>
+  </si>
+  <si>
+    <t>--no-ff</t>
+  </si>
+  <si>
+    <t>ファストフォワードせず必ずコミットを作る</t>
+  </si>
+  <si>
+    <t>--abort</t>
+  </si>
+  <si>
+    <t>コンフリクト発生時にマージを中止する</t>
+  </si>
+  <si>
+    <t>引数</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>git add .</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>git commit-m "コメント"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>git push</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>find . -name .DS_Store -delete</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">git add </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>webgame/src</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>送信待ちのリストの削除</t>
+    <t>単語</t>
     <rPh sb="0" eb="2">
-      <t>ソウシn</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t xml:space="preserve">マチ </t>
+      <t>タンゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>一部をリスト化</t>
-    <rPh sb="0" eb="2">
-      <t>イチブ</t>
+    <t>ショート
+ハンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強制的に送信（上書き）</t>
+  </si>
+  <si>
+    <t>--set-upstream</t>
+  </si>
+  <si>
+    <t>送信先をデフォルトとして登録</t>
+  </si>
+  <si>
+    <t>リモートのブランチを削除</t>
+  </si>
+  <si>
+    <t>--rebase</t>
+  </si>
+  <si>
+    <t>マージではなくリベースで取り込む</t>
+  </si>
+  <si>
+    <t>--no-commit</t>
+  </si>
+  <si>
+    <t>取り込むがコミットはしない</t>
+  </si>
+  <si>
+    <t>--prune</t>
+  </si>
+  <si>
+    <t>削除されたリモート枝の情報を整理</t>
+  </si>
+  <si>
+    <t>全てのリモートから情報を取得</t>
+  </si>
+  <si>
+    <t>--depth</t>
+  </si>
+  <si>
+    <t>履歴を制限して取得（軽量化）</t>
+  </si>
+  <si>
+    <t>特定のブランチだけをクローン</t>
+  </si>
+  <si>
+    <t>--verbose</t>
+  </si>
+  <si>
+    <t>登録されているURLを詳細に表示</t>
+  </si>
+  <si>
+    <t>--add</t>
+  </si>
+  <si>
+    <t>新しいリモートリポジトリを追加</t>
+  </si>
+  <si>
+    <t>--hard</t>
+  </si>
+  <si>
+    <t>ファイルもコミットも全て指定の状態に戻す</t>
+  </si>
+  <si>
+    <t>--soft</t>
+  </si>
+  <si>
+    <t>ファイルは残したままコミットだけ取消す</t>
+  </si>
+  <si>
+    <t>打ち消しを記録せず、ファイルだけ戻す</t>
+  </si>
+  <si>
+    <t>--edit</t>
+  </si>
+  <si>
+    <t>打ち消しメッセージを編集する</t>
+  </si>
+  <si>
+    <t>現在の状態を一時保存する</t>
+  </si>
+  <si>
+    <t>避難させたリストを見る</t>
+  </si>
+  <si>
+    <t>--pop</t>
+  </si>
+  <si>
+    <t>最新の避難データを取り出して削除</t>
+  </si>
+  <si>
+    <t>--push (or save)</t>
+  </si>
+  <si>
+    <t>--help</t>
+  </si>
+  <si>
+    <t>全オプションの解説書（マニュアル）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>コマンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-A</t>
+  </si>
+  <si>
+    <t>-u</t>
+  </si>
+  <si>
+    <t>-n</t>
+  </si>
+  <si>
+    <t>-m</t>
+  </si>
+  <si>
+    <t>-a</t>
+  </si>
+  <si>
+    <t>-f</t>
+  </si>
+  <si>
+    <t>-d</t>
+  </si>
+  <si>
+    <t>-s</t>
+  </si>
+  <si>
+    <t>-b</t>
+  </si>
+  <si>
+    <t>-g</t>
+  </si>
+  <si>
+    <t>-c</t>
+  </si>
+  <si>
+    <t>-r</t>
+  </si>
+  <si>
+    <t>-p</t>
+  </si>
+  <si>
+    <t>-v</t>
+  </si>
+  <si>
+    <t>-e</t>
+  </si>
+  <si>
+    <t>-l</t>
+  </si>
+  <si>
+    <t>2. 過去に戻る・確認する
+3. 枝分かれ（ブランチ）と合流</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"メッセージ"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マージ</t>
+    <rPh sb="3" eb="5">
+      <t>サギョウ</t>
     </rPh>
-    <rPh sb="6" eb="7">
-      <t xml:space="preserve">カ </t>
+    <rPh sb="10" eb="13">
+      <t>ハンエイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全てをリスト化</t>
-    <rPh sb="0" eb="1">
-      <t>スベテ</t>
+    <t>(なし)</t>
+  </si>
+  <si>
+    <t>(なし)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5. 困った時・やり直したい時</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行コマンド</t>
+    <rPh sb="0" eb="2">
+      <t>ジッコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>基本的にはこれを使う</t>
-    <rPh sb="0" eb="3">
-      <t>キホn</t>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Macの場合勝手に作られる.DS_Storeファイルを削除する。</t>
-    <rPh sb="6" eb="8">
-      <t>カッテ</t>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
     </rPh>
-    <rPh sb="27" eb="29">
-      <t>サクジョ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記入内容</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクション
+順番</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0.困った時</t>
+    <rPh sb="2" eb="3">
+      <t>コマッタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【2.】ファイルを過去の状態に戻す
+【3.】ブランチを切り替える</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【2.】失敗した時に以前の版を出す
+【3.】別の道（枝）へ移動する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git remote add origin https://github.com/ユーザーID/リポジトリ名.git</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション / フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数1</t>
+    <rPh sb="0" eb="2">
+      <t>ヒキスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引数2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業ブランチ:反映先ブランチ
+例）master:main</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>origin
+※ 登録済みのリモートリポジトリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ローカルフォルダを指定
+・「.」で全て指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">git add . </t>
+  </si>
+  <si>
+    <t>git add webgame/src</t>
+  </si>
+  <si>
+    <t>git add docs</t>
+  </si>
+  <si>
+    <t>git commit -m "コメント"</t>
+  </si>
+  <si>
+    <t>1.add</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.commit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.push</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初回：安全コマンド集（順番に実行）</t>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1667,7 +2225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1779,21 +2337,135 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFF0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFF9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1900,6 +2572,486 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1909,7 +3061,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1975,6 +3127,519 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1985,6 +3650,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF9FFFF"/>
+      <color rgb="FFEFFFFF"/>
+      <color rgb="FFFFFFF0"/>
+      <color rgb="FFFFFFF9"/>
+      <color rgb="FFFFFFE9"/>
+      <color rgb="FFF9FFF3"/>
+      <color rgb="FFFFFED6"/>
       <color rgb="FFFBFFCB"/>
     </mruColors>
   </colors>
@@ -3777,7 +5449,7 @@
     </row>
     <row r="81" spans="2:3">
       <c r="C81" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="85" spans="2:3" ht="40">
@@ -3991,301 +5663,365 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29287DF5-21CC-7D4B-BB9B-06DAB6E5204E}">
-  <dimension ref="B2:Y56"/>
+  <dimension ref="B2:Y55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.7109375" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:17">
-      <c r="B2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17">
-      <c r="B4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="C6" t="s">
-        <v>310</v>
-      </c>
-      <c r="P6" t="s">
+    <row r="2" spans="2:12">
+      <c r="B2" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="185" t="s">
+        <v>484</v>
+      </c>
+      <c r="C3" s="186"/>
+      <c r="D3" s="186"/>
+      <c r="E3" s="177" t="s">
+        <v>480</v>
+      </c>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="179"/>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="187"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="175" t="s">
+        <v>481</v>
+      </c>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="180"/>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="189"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="181" t="s">
+        <v>482</v>
+      </c>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="183"/>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="191" t="s">
+        <v>485</v>
+      </c>
+      <c r="C6" s="192"/>
+      <c r="D6" s="192"/>
+      <c r="E6" s="184" t="s">
+        <v>483</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="191" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="184" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="7" spans="2:17">
-      <c r="C7" t="s">
-        <v>308</v>
-      </c>
-      <c r="P7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17">
-      <c r="C8" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17">
-      <c r="C9" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17">
-      <c r="P10" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17">
-      <c r="P11" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" ht="31">
-      <c r="B25" s="11" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="24" spans="2:25" ht="31">
+      <c r="B24" s="11" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25">
+      <c r="B26" s="15" t="s">
         <v>272</v>
       </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="17"/>
     </row>
     <row r="27" spans="2:25">
-      <c r="B27" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="15" t="s">
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="17"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="20"/>
     </row>
     <row r="28" spans="2:25">
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="21" t="s">
+      <c r="B28" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="20"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="17"/>
     </row>
     <row r="29" spans="2:25">
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="15" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="17"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="20"/>
     </row>
     <row r="30" spans="2:25">
-      <c r="B30" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="21" t="s">
+      <c r="B30" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="20"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="17"/>
     </row>
     <row r="31" spans="2:25">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="15" t="s">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="17"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="20"/>
     </row>
     <row r="32" spans="2:25">
-      <c r="B32" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="21" t="s">
+      <c r="B32" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="20"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="17"/>
     </row>
     <row r="33" spans="2:25">
-      <c r="B33" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="15" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="17"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="20"/>
     </row>
     <row r="34" spans="2:25">
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="21" t="s">
+      <c r="B34" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="20"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="14"/>
     </row>
     <row r="35" spans="2:25">
       <c r="B35" s="12" t="s">
@@ -4301,7 +6037,7 @@
       <c r="J35" s="13"/>
       <c r="K35" s="14"/>
       <c r="L35" s="12" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
@@ -4331,7 +6067,7 @@
       <c r="J36" s="13"/>
       <c r="K36" s="14"/>
       <c r="L36" s="12" t="s">
-        <v>151</v>
+        <v>289</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
@@ -4348,153 +6084,2399 @@
       <c r="Y36" s="14"/>
     </row>
     <row r="37" spans="2:25">
-      <c r="B37" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="12" t="s">
+      <c r="B37" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="14"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="17"/>
     </row>
     <row r="38" spans="2:25">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="19"/>
+      <c r="Y38" s="20"/>
+    </row>
+    <row r="39" spans="2:25">
+      <c r="B39" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="17"/>
-    </row>
-    <row r="39" spans="2:25">
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="21" t="s">
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="14"/>
+    </row>
+    <row r="42" spans="2:25" ht="24">
+      <c r="B42" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="20"/>
-    </row>
-    <row r="40" spans="2:25">
-      <c r="B40" s="12" t="s">
+    </row>
+    <row r="44" spans="2:25">
+      <c r="B44" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
-      <c r="R40" s="13"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="13"/>
-      <c r="U40" s="13"/>
-      <c r="V40" s="13"/>
-      <c r="W40" s="13"/>
-      <c r="X40" s="13"/>
-      <c r="Y40" s="14"/>
-    </row>
-    <row r="43" spans="2:25" ht="24">
-      <c r="B43" s="9" t="s">
+    </row>
+    <row r="46" spans="2:25">
+      <c r="B46" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="2:25">
-      <c r="B45" s="1" t="s">
+    <row r="48" spans="2:25">
+      <c r="B48" s="8" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="47" spans="2:25">
-      <c r="B47" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="8" t="s">
-        <v>297</v>
-      </c>
+    <row r="52" spans="2:2">
+      <c r="B52" s="1"/>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="1"/>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="1"/>
+    <row r="55" spans="2:2">
+      <c r="B55" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1A19F4-4813-0246-9D2F-23C838085AF4}">
+  <dimension ref="B1:Q118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="3.7109375" style="27" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36" style="3" customWidth="1"/>
+    <col min="15" max="15" width="41.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.7109375" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17">
+      <c r="I1" s="26"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="2:17">
+      <c r="B2" s="71" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>468</v>
+      </c>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="76" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="76" t="s">
+        <v>465</v>
+      </c>
+      <c r="P2" s="78"/>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="B3" s="66"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="79" t="s">
+        <v>437</v>
+      </c>
+      <c r="H3" s="80"/>
+      <c r="I3" s="156" t="s">
+        <v>474</v>
+      </c>
+      <c r="J3" s="155"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="155" t="s">
+        <v>401</v>
+      </c>
+      <c r="M3" s="155"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="89" t="s">
+        <v>298</v>
+      </c>
+      <c r="P3" s="89" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="59" customHeight="1">
+      <c r="B4" s="65"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="84" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="84" t="s">
+        <v>456</v>
+      </c>
+      <c r="F4" s="85"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="86" t="s">
+        <v>402</v>
+      </c>
+      <c r="J4" s="87" t="s">
+        <v>403</v>
+      </c>
+      <c r="K4" s="164" t="s">
+        <v>467</v>
+      </c>
+      <c r="L4" s="157" t="s">
+        <v>457</v>
+      </c>
+      <c r="M4" s="167" t="s">
+        <v>475</v>
+      </c>
+      <c r="N4" s="88" t="s">
+        <v>476</v>
+      </c>
+      <c r="O4" s="90"/>
+      <c r="P4" s="90"/>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="B5" s="105" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="91" t="s">
+        <v>469</v>
+      </c>
+      <c r="D5" s="54"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="H5" s="103" t="s">
+        <v>469</v>
+      </c>
+      <c r="I5" s="104" t="s">
+        <v>434</v>
+      </c>
+      <c r="J5" s="146" t="s">
+        <v>461</v>
+      </c>
+      <c r="K5" s="158"/>
+      <c r="L5" s="158" t="s">
+        <v>458</v>
+      </c>
+      <c r="M5" s="168"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" spans="2:17" ht="42">
+      <c r="B6" s="105" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>339</v>
+      </c>
+      <c r="D6" s="54">
+        <v>1</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="159"/>
+      <c r="L6" s="159" t="s">
+        <v>455</v>
+      </c>
+      <c r="M6" s="169"/>
+      <c r="N6" s="46" t="s">
+        <v>479</v>
+      </c>
+      <c r="O6" s="96" t="s">
+        <v>300</v>
+      </c>
+      <c r="P6" s="97" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q6" s="24"/>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="B7" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" s="55">
+        <v>1</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="I7" s="136" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" s="147" t="s">
+        <v>438</v>
+      </c>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="139" t="s">
+        <v>359</v>
+      </c>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="24"/>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="B8" s="107" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" s="93" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="56">
+        <v>1</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>339</v>
+      </c>
+      <c r="I8" s="140" t="s">
+        <v>360</v>
+      </c>
+      <c r="J8" s="148" t="s">
+        <v>440</v>
+      </c>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="143" t="s">
+        <v>361</v>
+      </c>
+      <c r="P8" s="142"/>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="B9" s="105" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="100" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="54">
+        <v>2</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="159"/>
+      <c r="L9" s="159"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="96" t="s">
+        <v>302</v>
+      </c>
+      <c r="P9" s="97" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="B10" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" s="55">
+        <v>2</v>
+      </c>
+      <c r="E10" s="60"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="I10" s="144" t="s">
+        <v>362</v>
+      </c>
+      <c r="J10" s="149" t="s">
+        <v>441</v>
+      </c>
+      <c r="K10" s="137" t="s">
+        <v>459</v>
+      </c>
+      <c r="L10" s="137"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="138"/>
+      <c r="O10" s="139" t="s">
+        <v>363</v>
+      </c>
+      <c r="P10" s="138"/>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="B11" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="55">
+        <v>2</v>
+      </c>
+      <c r="E11" s="60"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="I11" s="136" t="s">
+        <v>364</v>
+      </c>
+      <c r="J11" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="139" t="s">
+        <v>365</v>
+      </c>
+      <c r="P11" s="138"/>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12" s="107" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="56">
+        <v>2</v>
+      </c>
+      <c r="E12" s="61"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" s="140" t="s">
+        <v>358</v>
+      </c>
+      <c r="J12" s="148" t="s">
+        <v>442</v>
+      </c>
+      <c r="K12" s="141"/>
+      <c r="L12" s="141"/>
+      <c r="M12" s="140"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="143" t="s">
+        <v>366</v>
+      </c>
+      <c r="P12" s="142"/>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="B13" s="94" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>341</v>
+      </c>
+      <c r="D13" s="57">
+        <v>3</v>
+      </c>
+      <c r="E13" s="62">
+        <v>2</v>
+      </c>
+      <c r="F13" s="37"/>
+      <c r="G13" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="39"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="165"/>
+      <c r="L13" s="40" t="s">
+        <v>455</v>
+      </c>
+      <c r="M13" s="170"/>
+      <c r="N13" s="40" t="s">
+        <v>462</v>
+      </c>
+      <c r="O13" s="98" t="s">
+        <v>305</v>
+      </c>
+      <c r="P13" s="98" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q13" s="24"/>
+    </row>
+    <row r="14" spans="2:17" ht="42">
+      <c r="B14" s="95"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="166"/>
+      <c r="L14" s="45" t="s">
+        <v>460</v>
+      </c>
+      <c r="M14" s="174" t="s">
+        <v>478</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>477</v>
+      </c>
+      <c r="O14" s="99"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="24"/>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="B15" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="55">
+        <v>3</v>
+      </c>
+      <c r="E15" s="60">
+        <v>2</v>
+      </c>
+      <c r="F15" s="49"/>
+      <c r="G15" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="I15" s="144" t="s">
+        <v>386</v>
+      </c>
+      <c r="J15" s="149" t="s">
+        <v>443</v>
+      </c>
+      <c r="K15" s="137"/>
+      <c r="L15" s="137"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="139" t="s">
+        <v>404</v>
+      </c>
+      <c r="P15" s="138"/>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="B16" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="55">
+        <v>3</v>
+      </c>
+      <c r="E16" s="60">
+        <v>2</v>
+      </c>
+      <c r="F16" s="49"/>
+      <c r="G16" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="I16" s="144" t="s">
+        <v>405</v>
+      </c>
+      <c r="J16" s="149" t="s">
+        <v>439</v>
+      </c>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="139" t="s">
+        <v>406</v>
+      </c>
+      <c r="P16" s="138"/>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" s="107" t="s">
+        <v>316</v>
+      </c>
+      <c r="C17" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" s="56">
+        <v>3</v>
+      </c>
+      <c r="E17" s="61">
+        <v>2</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="I17" s="140" t="s">
+        <v>390</v>
+      </c>
+      <c r="J17" s="148" t="s">
+        <v>444</v>
+      </c>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="140"/>
+      <c r="N17" s="142"/>
+      <c r="O17" s="143" t="s">
+        <v>407</v>
+      </c>
+      <c r="P17" s="142"/>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="B18" s="105" t="s">
+        <v>316</v>
+      </c>
+      <c r="C18" s="100" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="54"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="159"/>
+      <c r="L18" s="159"/>
+      <c r="M18" s="169"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="96" t="s">
+        <v>307</v>
+      </c>
+      <c r="P18" s="97" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="B19" s="106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C19" s="92" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="I19" s="144" t="s">
+        <v>367</v>
+      </c>
+      <c r="J19" s="149" t="s">
+        <v>445</v>
+      </c>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="139" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" s="138"/>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="B20" s="107" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="I20" s="140" t="s">
+        <v>369</v>
+      </c>
+      <c r="J20" s="148" t="s">
+        <v>446</v>
+      </c>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="140"/>
+      <c r="N20" s="142"/>
+      <c r="O20" s="143" t="s">
+        <v>370</v>
+      </c>
+      <c r="P20" s="142"/>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="B21" s="105" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" s="100" t="s">
+        <v>343</v>
+      </c>
+      <c r="D21" s="54"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="I21" s="34"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="159"/>
+      <c r="L21" s="159"/>
+      <c r="M21" s="169"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="96" t="s">
+        <v>309</v>
+      </c>
+      <c r="P21" s="97" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q21" s="24"/>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22" s="106" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" s="92" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="55"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="I22" s="136" t="s">
+        <v>371</v>
+      </c>
+      <c r="J22" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="138"/>
+      <c r="O22" s="139" t="s">
+        <v>372</v>
+      </c>
+      <c r="P22" s="138"/>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="B23" s="106" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>343</v>
+      </c>
+      <c r="D23" s="55"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="I23" s="136" t="s">
+        <v>373</v>
+      </c>
+      <c r="J23" s="147" t="s">
+        <v>447</v>
+      </c>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="139" t="s">
+        <v>374</v>
+      </c>
+      <c r="P23" s="138"/>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="B24" s="107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="93" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="56"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="I24" s="140" t="s">
+        <v>358</v>
+      </c>
+      <c r="J24" s="148" t="s">
+        <v>442</v>
+      </c>
+      <c r="K24" s="141"/>
+      <c r="L24" s="141"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="142"/>
+      <c r="O24" s="143" t="s">
+        <v>375</v>
+      </c>
+      <c r="P24" s="142"/>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="B25" s="105" t="s">
+        <v>315</v>
+      </c>
+      <c r="C25" s="100" t="s">
+        <v>344</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="I25" s="34"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="159"/>
+      <c r="L25" s="159"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="96" t="s">
+        <v>311</v>
+      </c>
+      <c r="P25" s="97" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q25" s="24"/>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="B26" s="106" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="92" t="s">
+        <v>344</v>
+      </c>
+      <c r="D26" s="55"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="I26" s="136" t="s">
+        <v>382</v>
+      </c>
+      <c r="J26" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K26" s="137"/>
+      <c r="L26" s="137"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="138"/>
+      <c r="O26" s="139" t="s">
+        <v>383</v>
+      </c>
+      <c r="P26" s="138"/>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="B27" s="107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C27" s="93" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" s="56"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>344</v>
+      </c>
+      <c r="I27" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="J27" s="148" t="s">
+        <v>440</v>
+      </c>
+      <c r="K27" s="141"/>
+      <c r="L27" s="141"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="142"/>
+      <c r="O27" s="143" t="s">
+        <v>377</v>
+      </c>
+      <c r="P27" s="142"/>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="B28" s="105" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="D28" s="54"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="159"/>
+      <c r="L28" s="159"/>
+      <c r="M28" s="169"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="96" t="s">
+        <v>313</v>
+      </c>
+      <c r="P28" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q28" s="24"/>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29" s="106" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="92" t="s">
+        <v>345</v>
+      </c>
+      <c r="D29" s="55"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="I29" s="136" t="s">
+        <v>378</v>
+      </c>
+      <c r="J29" s="147" t="s">
+        <v>436</v>
+      </c>
+      <c r="K29" s="137"/>
+      <c r="L29" s="137"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="139" t="s">
+        <v>379</v>
+      </c>
+      <c r="P29" s="138"/>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="B30" s="107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D30" s="56"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H30" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="I30" s="140" t="s">
+        <v>380</v>
+      </c>
+      <c r="J30" s="148" t="s">
+        <v>443</v>
+      </c>
+      <c r="K30" s="141"/>
+      <c r="L30" s="141"/>
+      <c r="M30" s="140"/>
+      <c r="N30" s="142"/>
+      <c r="O30" s="143" t="s">
+        <v>381</v>
+      </c>
+      <c r="P30" s="142"/>
+    </row>
+    <row r="31" spans="2:17" ht="42">
+      <c r="B31" s="108" t="s">
+        <v>454</v>
+      </c>
+      <c r="C31" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112">
+        <v>1</v>
+      </c>
+      <c r="F31" s="113"/>
+      <c r="G31" s="114" t="s">
+        <v>357</v>
+      </c>
+      <c r="H31" s="115" t="s">
+        <v>346</v>
+      </c>
+      <c r="I31" s="115"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="160"/>
+      <c r="M31" s="171"/>
+      <c r="N31" s="116"/>
+      <c r="O31" s="117" t="s">
+        <v>471</v>
+      </c>
+      <c r="P31" s="118" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="42">
+      <c r="B32" s="109" t="s">
+        <v>454</v>
+      </c>
+      <c r="C32" s="92" t="s">
+        <v>346</v>
+      </c>
+      <c r="D32" s="119"/>
+      <c r="E32" s="120">
+        <v>1</v>
+      </c>
+      <c r="F32" s="121"/>
+      <c r="G32" s="122" t="s">
+        <v>357</v>
+      </c>
+      <c r="H32" s="123" t="s">
+        <v>346</v>
+      </c>
+      <c r="I32" s="129" t="s">
+        <v>369</v>
+      </c>
+      <c r="J32" s="151" t="s">
+        <v>446</v>
+      </c>
+      <c r="K32" s="161"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="172"/>
+      <c r="N32" s="130"/>
+      <c r="O32" s="131" t="s">
+        <v>385</v>
+      </c>
+      <c r="P32" s="130"/>
+    </row>
+    <row r="33" spans="2:17" ht="42">
+      <c r="B33" s="110" t="s">
+        <v>454</v>
+      </c>
+      <c r="C33" s="93" t="s">
+        <v>346</v>
+      </c>
+      <c r="D33" s="124"/>
+      <c r="E33" s="125">
+        <v>1</v>
+      </c>
+      <c r="F33" s="126"/>
+      <c r="G33" s="127" t="s">
+        <v>357</v>
+      </c>
+      <c r="H33" s="128" t="s">
+        <v>346</v>
+      </c>
+      <c r="I33" s="132" t="s">
+        <v>386</v>
+      </c>
+      <c r="J33" s="152" t="s">
+        <v>443</v>
+      </c>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
+      <c r="M33" s="132"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="135" t="s">
+        <v>387</v>
+      </c>
+      <c r="P33" s="134"/>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="B34" s="105" t="s">
+        <v>317</v>
+      </c>
+      <c r="C34" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="D34" s="54"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H34" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="I34" s="34"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="159"/>
+      <c r="L34" s="159"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="96" t="s">
+        <v>318</v>
+      </c>
+      <c r="P34" s="97" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q34" s="24"/>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="B35" s="106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C35" s="92" t="s">
+        <v>347</v>
+      </c>
+      <c r="D35" s="55"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="I35" s="136" t="s">
+        <v>388</v>
+      </c>
+      <c r="J35" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K35" s="137"/>
+      <c r="L35" s="137"/>
+      <c r="M35" s="136"/>
+      <c r="N35" s="138"/>
+      <c r="O35" s="139" t="s">
+        <v>389</v>
+      </c>
+      <c r="P35" s="138"/>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="B36" s="106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>347</v>
+      </c>
+      <c r="D36" s="55"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="I36" s="136" t="s">
+        <v>390</v>
+      </c>
+      <c r="J36" s="147" t="s">
+        <v>444</v>
+      </c>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
+      <c r="M36" s="136"/>
+      <c r="N36" s="138"/>
+      <c r="O36" s="139" t="s">
+        <v>391</v>
+      </c>
+      <c r="P36" s="138"/>
+    </row>
+    <row r="37" spans="2:17">
+      <c r="B37" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" s="93" t="s">
+        <v>347</v>
+      </c>
+      <c r="D37" s="56"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="I37" s="140" t="s">
+        <v>392</v>
+      </c>
+      <c r="J37" s="148" t="s">
+        <v>441</v>
+      </c>
+      <c r="K37" s="141"/>
+      <c r="L37" s="141"/>
+      <c r="M37" s="140"/>
+      <c r="N37" s="142"/>
+      <c r="O37" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="P37" s="142"/>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="B38" s="105" t="s">
+        <v>317</v>
+      </c>
+      <c r="C38" s="100" t="s">
+        <v>348</v>
+      </c>
+      <c r="D38" s="54"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="I38" s="34"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="159"/>
+      <c r="L38" s="159"/>
+      <c r="M38" s="169"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="96" t="s">
+        <v>321</v>
+      </c>
+      <c r="P38" s="97" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q38" s="24"/>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="B39" s="106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C39" s="92" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="55"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H39" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="I39" s="136" t="s">
+        <v>397</v>
+      </c>
+      <c r="J39" s="147" t="s">
+        <v>440</v>
+      </c>
+      <c r="K39" s="137"/>
+      <c r="L39" s="137"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="138"/>
+      <c r="O39" s="139" t="s">
+        <v>398</v>
+      </c>
+      <c r="P39" s="138"/>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="B40" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C40" s="93" t="s">
+        <v>348</v>
+      </c>
+      <c r="D40" s="56"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H40" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="I40" s="140" t="s">
+        <v>399</v>
+      </c>
+      <c r="J40" s="148" t="s">
+        <v>461</v>
+      </c>
+      <c r="K40" s="141"/>
+      <c r="L40" s="141"/>
+      <c r="M40" s="140"/>
+      <c r="N40" s="142"/>
+      <c r="O40" s="143" t="s">
+        <v>400</v>
+      </c>
+      <c r="P40" s="142"/>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="B41" s="105" t="s">
+        <v>317</v>
+      </c>
+      <c r="C41" s="100" t="s">
+        <v>349</v>
+      </c>
+      <c r="D41" s="54"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H41" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="I41" s="34"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="159"/>
+      <c r="L41" s="159"/>
+      <c r="M41" s="169"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="96" t="s">
+        <v>320</v>
+      </c>
+      <c r="P41" s="97" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="B42" s="106" t="s">
+        <v>317</v>
+      </c>
+      <c r="C42" s="92" t="s">
+        <v>349</v>
+      </c>
+      <c r="D42" s="55"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H42" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="I42" s="136" t="s">
+        <v>394</v>
+      </c>
+      <c r="J42" s="147" t="s">
+        <v>448</v>
+      </c>
+      <c r="K42" s="137"/>
+      <c r="L42" s="137"/>
+      <c r="M42" s="136"/>
+      <c r="N42" s="138"/>
+      <c r="O42" s="139" t="s">
+        <v>385</v>
+      </c>
+      <c r="P42" s="138"/>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="B43" s="107" t="s">
+        <v>317</v>
+      </c>
+      <c r="C43" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D43" s="56"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H43" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="I43" s="140" t="s">
+        <v>395</v>
+      </c>
+      <c r="J43" s="148" t="s">
+        <v>444</v>
+      </c>
+      <c r="K43" s="141"/>
+      <c r="L43" s="141"/>
+      <c r="M43" s="140"/>
+      <c r="N43" s="142"/>
+      <c r="O43" s="143" t="s">
+        <v>396</v>
+      </c>
+      <c r="P43" s="142"/>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="B44" s="105" t="s">
+        <v>323</v>
+      </c>
+      <c r="C44" s="100" t="s">
+        <v>350</v>
+      </c>
+      <c r="D44" s="54"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="I44" s="34"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="159"/>
+      <c r="L44" s="159"/>
+      <c r="M44" s="169"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="96" t="s">
+        <v>324</v>
+      </c>
+      <c r="P44" s="97" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="B45" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="C45" s="92" t="s">
+        <v>350</v>
+      </c>
+      <c r="D45" s="55"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="I45" s="136" t="s">
+        <v>408</v>
+      </c>
+      <c r="J45" s="147" t="s">
+        <v>449</v>
+      </c>
+      <c r="K45" s="137"/>
+      <c r="L45" s="137"/>
+      <c r="M45" s="136"/>
+      <c r="N45" s="138"/>
+      <c r="O45" s="139" t="s">
+        <v>409</v>
+      </c>
+      <c r="P45" s="138"/>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="B46" s="107" t="s">
+        <v>323</v>
+      </c>
+      <c r="C46" s="93" t="s">
+        <v>350</v>
+      </c>
+      <c r="D46" s="56"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H46" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="I46" s="140" t="s">
+        <v>410</v>
+      </c>
+      <c r="J46" s="148" t="s">
+        <v>440</v>
+      </c>
+      <c r="K46" s="141"/>
+      <c r="L46" s="141"/>
+      <c r="M46" s="140"/>
+      <c r="N46" s="142"/>
+      <c r="O46" s="143" t="s">
+        <v>411</v>
+      </c>
+      <c r="P46" s="142"/>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="B47" s="105" t="s">
+        <v>323</v>
+      </c>
+      <c r="C47" s="100" t="s">
+        <v>351</v>
+      </c>
+      <c r="D47" s="54"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="I47" s="34"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="159"/>
+      <c r="M47" s="169"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="96" t="s">
+        <v>326</v>
+      </c>
+      <c r="P47" s="97" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="B48" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="C48" s="92" t="s">
+        <v>351</v>
+      </c>
+      <c r="D48" s="55"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H48" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="I48" s="136" t="s">
+        <v>412</v>
+      </c>
+      <c r="J48" s="147" t="s">
+        <v>450</v>
+      </c>
+      <c r="K48" s="137"/>
+      <c r="L48" s="137"/>
+      <c r="M48" s="136"/>
+      <c r="N48" s="138"/>
+      <c r="O48" s="139" t="s">
+        <v>413</v>
+      </c>
+      <c r="P48" s="138"/>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="B49" s="107" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49" s="93" t="s">
+        <v>351</v>
+      </c>
+      <c r="D49" s="56"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H49" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="I49" s="140" t="s">
+        <v>358</v>
+      </c>
+      <c r="J49" s="148" t="s">
+        <v>442</v>
+      </c>
+      <c r="K49" s="141"/>
+      <c r="L49" s="141"/>
+      <c r="M49" s="140"/>
+      <c r="N49" s="142"/>
+      <c r="O49" s="143" t="s">
+        <v>414</v>
+      </c>
+      <c r="P49" s="142"/>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="B50" s="105" t="s">
+        <v>323</v>
+      </c>
+      <c r="C50" s="100" t="s">
+        <v>352</v>
+      </c>
+      <c r="D50" s="54"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="I50" s="34"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="159"/>
+      <c r="L50" s="159"/>
+      <c r="M50" s="169"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="96" t="s">
+        <v>328</v>
+      </c>
+      <c r="P50" s="97" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
+      <c r="B51" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>352</v>
+      </c>
+      <c r="D51" s="55"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H51" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="I51" s="136" t="s">
+        <v>415</v>
+      </c>
+      <c r="J51" s="147" t="s">
+        <v>444</v>
+      </c>
+      <c r="K51" s="137"/>
+      <c r="L51" s="137"/>
+      <c r="M51" s="136"/>
+      <c r="N51" s="138"/>
+      <c r="O51" s="139" t="s">
+        <v>416</v>
+      </c>
+      <c r="P51" s="138"/>
+    </row>
+    <row r="52" spans="2:17">
+      <c r="B52" s="107" t="s">
+        <v>323</v>
+      </c>
+      <c r="C52" s="93" t="s">
+        <v>352</v>
+      </c>
+      <c r="D52" s="56"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H52" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="I52" s="140" t="s">
+        <v>369</v>
+      </c>
+      <c r="J52" s="148" t="s">
+        <v>446</v>
+      </c>
+      <c r="K52" s="141"/>
+      <c r="L52" s="141"/>
+      <c r="M52" s="140"/>
+      <c r="N52" s="142"/>
+      <c r="O52" s="143" t="s">
+        <v>417</v>
+      </c>
+      <c r="P52" s="142"/>
+    </row>
+    <row r="53" spans="2:17">
+      <c r="B53" s="105" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="100" t="s">
+        <v>353</v>
+      </c>
+      <c r="D53" s="54"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="I53" s="34"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="159"/>
+      <c r="L53" s="159"/>
+      <c r="M53" s="169"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="96" t="s">
+        <v>330</v>
+      </c>
+      <c r="P53" s="97" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
+      <c r="B54" s="106" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" s="92" t="s">
+        <v>353</v>
+      </c>
+      <c r="D54" s="55"/>
+      <c r="E54" s="60"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H54" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="I54" s="136" t="s">
+        <v>418</v>
+      </c>
+      <c r="J54" s="147" t="s">
+        <v>451</v>
+      </c>
+      <c r="K54" s="137"/>
+      <c r="L54" s="137"/>
+      <c r="M54" s="136"/>
+      <c r="N54" s="138"/>
+      <c r="O54" s="139" t="s">
+        <v>419</v>
+      </c>
+      <c r="P54" s="138"/>
+    </row>
+    <row r="55" spans="2:17">
+      <c r="B55" s="107" t="s">
+        <v>323</v>
+      </c>
+      <c r="C55" s="93" t="s">
+        <v>353</v>
+      </c>
+      <c r="D55" s="56"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H55" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="I55" s="140" t="s">
+        <v>420</v>
+      </c>
+      <c r="J55" s="148" t="s">
+        <v>442</v>
+      </c>
+      <c r="K55" s="141"/>
+      <c r="L55" s="141"/>
+      <c r="M55" s="140"/>
+      <c r="N55" s="142"/>
+      <c r="O55" s="143" t="s">
+        <v>421</v>
+      </c>
+      <c r="P55" s="142"/>
+    </row>
+    <row r="56" spans="2:17">
+      <c r="B56" s="105" t="s">
+        <v>463</v>
+      </c>
+      <c r="C56" s="100" t="s">
+        <v>354</v>
+      </c>
+      <c r="D56" s="54"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="I56" s="34"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="159"/>
+      <c r="L56" s="159"/>
+      <c r="M56" s="169"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="96" t="s">
+        <v>333</v>
+      </c>
+      <c r="P56" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q56" s="24"/>
+    </row>
+    <row r="57" spans="2:17">
+      <c r="B57" s="106" t="s">
+        <v>332</v>
+      </c>
+      <c r="C57" s="92" t="s">
+        <v>354</v>
+      </c>
+      <c r="D57" s="55"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H57" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="I57" s="136" t="s">
+        <v>422</v>
+      </c>
+      <c r="J57" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K57" s="137"/>
+      <c r="L57" s="137"/>
+      <c r="M57" s="136"/>
+      <c r="N57" s="138"/>
+      <c r="O57" s="139" t="s">
+        <v>423</v>
+      </c>
+      <c r="P57" s="138"/>
+      <c r="Q57" s="24"/>
+    </row>
+    <row r="58" spans="2:17">
+      <c r="B58" s="107" t="s">
+        <v>332</v>
+      </c>
+      <c r="C58" s="93" t="s">
+        <v>354</v>
+      </c>
+      <c r="D58" s="56"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H58" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="I58" s="140" t="s">
+        <v>424</v>
+      </c>
+      <c r="J58" s="148" t="s">
+        <v>461</v>
+      </c>
+      <c r="K58" s="141"/>
+      <c r="L58" s="141"/>
+      <c r="M58" s="140"/>
+      <c r="N58" s="142"/>
+      <c r="O58" s="143" t="s">
+        <v>425</v>
+      </c>
+      <c r="P58" s="142"/>
+    </row>
+    <row r="59" spans="2:17">
+      <c r="B59" s="105" t="s">
+        <v>332</v>
+      </c>
+      <c r="C59" s="100" t="s">
+        <v>355</v>
+      </c>
+      <c r="D59" s="54"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H59" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="I59" s="34"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="159"/>
+      <c r="L59" s="159"/>
+      <c r="M59" s="169"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="96" t="s">
+        <v>335</v>
+      </c>
+      <c r="P59" s="97" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
+      <c r="B60" s="106" t="s">
+        <v>332</v>
+      </c>
+      <c r="C60" s="92" t="s">
+        <v>355</v>
+      </c>
+      <c r="D60" s="55"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H60" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="I60" s="136" t="s">
+        <v>410</v>
+      </c>
+      <c r="J60" s="147" t="s">
+        <v>440</v>
+      </c>
+      <c r="K60" s="137"/>
+      <c r="L60" s="137"/>
+      <c r="M60" s="136"/>
+      <c r="N60" s="138"/>
+      <c r="O60" s="139" t="s">
+        <v>426</v>
+      </c>
+      <c r="P60" s="138"/>
+    </row>
+    <row r="61" spans="2:17">
+      <c r="B61" s="107" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="93" t="s">
+        <v>355</v>
+      </c>
+      <c r="D61" s="56"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="52"/>
+      <c r="G61" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H61" s="53" t="s">
+        <v>355</v>
+      </c>
+      <c r="I61" s="140" t="s">
+        <v>427</v>
+      </c>
+      <c r="J61" s="148" t="s">
+        <v>452</v>
+      </c>
+      <c r="K61" s="141"/>
+      <c r="L61" s="141"/>
+      <c r="M61" s="140"/>
+      <c r="N61" s="142"/>
+      <c r="O61" s="143" t="s">
+        <v>428</v>
+      </c>
+      <c r="P61" s="142"/>
+    </row>
+    <row r="62" spans="2:17">
+      <c r="B62" s="105" t="s">
+        <v>332</v>
+      </c>
+      <c r="C62" s="100" t="s">
+        <v>356</v>
+      </c>
+      <c r="D62" s="54"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="I62" s="34"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="159"/>
+      <c r="L62" s="159"/>
+      <c r="M62" s="169"/>
+      <c r="N62" s="35"/>
+      <c r="O62" s="96" t="s">
+        <v>337</v>
+      </c>
+      <c r="P62" s="97" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
+      <c r="B63" s="106" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>356</v>
+      </c>
+      <c r="D63" s="55"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H63" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="I63" s="136" t="s">
+        <v>433</v>
+      </c>
+      <c r="J63" s="147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K63" s="137"/>
+      <c r="L63" s="137"/>
+      <c r="M63" s="136"/>
+      <c r="N63" s="138"/>
+      <c r="O63" s="139" t="s">
+        <v>429</v>
+      </c>
+      <c r="P63" s="138"/>
+    </row>
+    <row r="64" spans="2:17">
+      <c r="B64" s="106" t="s">
+        <v>332</v>
+      </c>
+      <c r="C64" s="92" t="s">
+        <v>356</v>
+      </c>
+      <c r="D64" s="55"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="H64" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="I64" s="136" t="s">
+        <v>388</v>
+      </c>
+      <c r="J64" s="147" t="s">
+        <v>453</v>
+      </c>
+      <c r="K64" s="137"/>
+      <c r="L64" s="137"/>
+      <c r="M64" s="136"/>
+      <c r="N64" s="138"/>
+      <c r="O64" s="139" t="s">
+        <v>430</v>
+      </c>
+      <c r="P64" s="138"/>
+    </row>
+    <row r="65" spans="2:16">
+      <c r="B65" s="107" t="s">
+        <v>463</v>
+      </c>
+      <c r="C65" s="93" t="s">
+        <v>356</v>
+      </c>
+      <c r="D65" s="56"/>
+      <c r="E65" s="61"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="51" t="s">
+        <v>357</v>
+      </c>
+      <c r="H65" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="I65" s="140" t="s">
+        <v>431</v>
+      </c>
+      <c r="J65" s="148" t="s">
+        <v>461</v>
+      </c>
+      <c r="K65" s="162"/>
+      <c r="L65" s="162"/>
+      <c r="M65" s="173"/>
+      <c r="N65" s="145"/>
+      <c r="O65" s="143" t="s">
+        <v>432</v>
+      </c>
+      <c r="P65" s="142"/>
+    </row>
+    <row r="66" spans="2:16">
+      <c r="I66" s="22"/>
+      <c r="J66" s="153"/>
+      <c r="K66" s="23"/>
+      <c r="L66" s="23"/>
+      <c r="M66" s="23"/>
+      <c r="N66" s="23"/>
+      <c r="O66" s="23"/>
+    </row>
+    <row r="67" spans="2:16">
+      <c r="I67" s="23"/>
+      <c r="J67" s="154"/>
+      <c r="K67" s="23"/>
+      <c r="L67" s="23"/>
+      <c r="M67" s="23"/>
+      <c r="N67" s="23"/>
+      <c r="O67" s="23"/>
+    </row>
+    <row r="68" spans="2:16">
+      <c r="I68" s="22"/>
+      <c r="J68" s="153"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
+    </row>
+    <row r="69" spans="2:16">
+      <c r="I69" s="23"/>
+      <c r="J69" s="154"/>
+      <c r="K69" s="23"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="23"/>
+      <c r="N69" s="23"/>
+      <c r="O69" s="23"/>
+    </row>
+    <row r="70" spans="2:16">
+      <c r="I70" s="22"/>
+      <c r="J70" s="153"/>
+      <c r="K70" s="23"/>
+      <c r="L70" s="23"/>
+      <c r="M70" s="23"/>
+      <c r="N70" s="23"/>
+      <c r="O70" s="23"/>
+    </row>
+    <row r="71" spans="2:16">
+      <c r="I71" s="23"/>
+      <c r="J71" s="154"/>
+      <c r="K71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+    </row>
+    <row r="72" spans="2:16">
+      <c r="I72" s="23"/>
+      <c r="J72" s="154"/>
+      <c r="K72" s="23"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="23"/>
+      <c r="N72" s="23"/>
+      <c r="O72" s="23"/>
+    </row>
+    <row r="73" spans="2:16">
+      <c r="I73" s="22"/>
+      <c r="J73" s="153"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="23"/>
+      <c r="N73" s="23"/>
+      <c r="O73" s="23"/>
+    </row>
+    <row r="74" spans="2:16">
+      <c r="I74" s="23"/>
+      <c r="J74" s="154"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
+    </row>
+    <row r="75" spans="2:16">
+      <c r="I75" s="22"/>
+      <c r="J75" s="153"/>
+      <c r="K75" s="23"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23"/>
+      <c r="N75" s="23"/>
+    </row>
+    <row r="76" spans="2:16">
+      <c r="I76" s="23"/>
+      <c r="J76" s="154"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="23"/>
+    </row>
+    <row r="78" spans="2:16">
+      <c r="C78" s="25"/>
+    </row>
+    <row r="79" spans="2:16">
+      <c r="C79" s="25"/>
+    </row>
+    <row r="80" spans="2:16">
+      <c r="C80" s="25"/>
+    </row>
+    <row r="81" spans="3:3">
+      <c r="C81" s="25"/>
+    </row>
+    <row r="82" spans="3:3">
+      <c r="C82" s="25"/>
+    </row>
+    <row r="83" spans="3:3">
+      <c r="C83" s="25"/>
+    </row>
+    <row r="84" spans="3:3">
+      <c r="C84" s="25"/>
+    </row>
+    <row r="85" spans="3:3">
+      <c r="C85" s="25"/>
+    </row>
+    <row r="86" spans="3:3">
+      <c r="C86" s="25"/>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="25"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="25"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="25"/>
+    </row>
+    <row r="90" spans="3:3">
+      <c r="C90" s="25"/>
+    </row>
+    <row r="91" spans="3:3">
+      <c r="C91" s="25"/>
+    </row>
+    <row r="92" spans="3:3">
+      <c r="C92" s="25"/>
+    </row>
+    <row r="93" spans="3:3">
+      <c r="C93" s="25"/>
+    </row>
+    <row r="94" spans="3:3">
+      <c r="C94" s="25"/>
+    </row>
+    <row r="95" spans="3:3">
+      <c r="C95" s="25"/>
+    </row>
+    <row r="96" spans="3:3">
+      <c r="C96" s="25"/>
+    </row>
+    <row r="97" spans="3:3">
+      <c r="C97" s="25"/>
+    </row>
+    <row r="98" spans="3:3">
+      <c r="C98" s="25"/>
+    </row>
+    <row r="99" spans="3:3">
+      <c r="C99" s="25"/>
+    </row>
+    <row r="100" spans="3:3">
+      <c r="C100" s="25"/>
+    </row>
+    <row r="101" spans="3:3">
+      <c r="C101" s="25"/>
+    </row>
+    <row r="102" spans="3:3">
+      <c r="C102" s="25"/>
+    </row>
+    <row r="103" spans="3:3">
+      <c r="C103" s="25"/>
+    </row>
+    <row r="104" spans="3:3">
+      <c r="C104" s="25"/>
+    </row>
+    <row r="105" spans="3:3">
+      <c r="C105" s="25"/>
+    </row>
+    <row r="106" spans="3:3">
+      <c r="C106" s="25"/>
+    </row>
+    <row r="107" spans="3:3">
+      <c r="C107" s="25"/>
+    </row>
+    <row r="108" spans="3:3">
+      <c r="C108" s="25"/>
+    </row>
+    <row r="109" spans="3:3">
+      <c r="C109" s="25"/>
+    </row>
+    <row r="110" spans="3:3">
+      <c r="C110" s="25"/>
+    </row>
+    <row r="111" spans="3:3">
+      <c r="C111" s="25"/>
+    </row>
+    <row r="112" spans="3:3">
+      <c r="C112" s="25"/>
+    </row>
+    <row r="113" spans="3:3">
+      <c r="C113" s="25"/>
+    </row>
+    <row r="114" spans="3:3">
+      <c r="C114" s="25"/>
+    </row>
+    <row r="115" spans="3:3">
+      <c r="C115" s="25"/>
+    </row>
+    <row r="116" spans="3:3">
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="3:3">
+      <c r="C117" s="25"/>
+    </row>
+    <row r="118" spans="3:3">
+      <c r="C118" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="D2:F3"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="G2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="C13:C14"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
